--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N73_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N73_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.62562993784068</v>
+        <v>4.97666486489911</v>
       </c>
       <c r="D2" t="n">
-        <v>29.48643127299684</v>
+        <v>4.791545081861987</v>
       </c>
       <c r="E2" t="n">
-        <v>8.274086493174627</v>
+        <v>1.344539055140877</v>
       </c>
       <c r="F2" t="n">
-        <v>9.805262585900531</v>
+        <v>1.593355170208836</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.81199202251903</v>
+        <v>5.981948703659342</v>
       </c>
       <c r="D3" t="n">
-        <v>46.70017667934189</v>
+        <v>7.588778710393058</v>
       </c>
       <c r="E3" t="n">
-        <v>8.274086493174627</v>
+        <v>1.344539055140877</v>
       </c>
       <c r="F3" t="n">
-        <v>9.805262585900531</v>
+        <v>1.593355170208836</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.00447653478995</v>
+        <v>2.763227436903368</v>
       </c>
       <c r="D4" t="n">
-        <v>23.58780462188224</v>
+        <v>3.833018251055864</v>
       </c>
       <c r="E4" t="n">
-        <v>8.274086493174627</v>
+        <v>1.344539055140877</v>
       </c>
       <c r="F4" t="n">
-        <v>9.805262585900531</v>
+        <v>1.593355170208836</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
